--- a/docs/sample-output/06-retail-pad-qsr/proforma.xlsx
+++ b/docs/sample-output/06-retail-pad-qsr/proforma.xlsx
@@ -264,7 +264,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 5 at 1.22% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 5 at 1.25% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Outparcel QSR with drive-thru · 5-Year Before-Tax</t>
@@ -1067,7 +1067,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>4048465.88</v>
+        <v>4046356.25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1075,7 +1075,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>0.050315355504490504</v>
+        <v>0.0503415881881384</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1083,7 +1083,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6">
-        <v>1443278.08622</v>
+        <v>1442526.0031249998</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1099,7 +1099,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>0.012197738477209842</v>
+        <v>0.012540741337868443</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1107,7 +1107,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>1.0627815685387687</v>
+        <v>1.064581655924115</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1123,7 +1123,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="7">
-        <v>0.012197738477209842</v>
+        <v>0.012540741337868443</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1138,7 +1138,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="6">
-        <v>4048465.88</v>
+        <v>4046356.25</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1154,7 +1154,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="6">
-        <v>26315.028220000004</v>
+        <v>26301.315625</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1162,7 +1162,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="6">
-        <v>4048465.88</v>
+        <v>4046356.25</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1170,7 +1170,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="6">
-        <v>-2631502.822</v>
+        <v>-2630131.5625</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1178,7 +1178,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="10">
-        <v>1443278.08622</v>
+        <v>1442526.0031249998</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1186,7 +1186,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>19.278408952380953</v>
+        <v>19.268363095238094</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1194,7 +1194,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>1445.8806714285713</v>
+        <v>1445.127232142857</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1209,7 +1209,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="6">
-        <v>2631502.822</v>
+        <v>2630131.5625</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1241,7 +1241,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="12">
-        <v>17768.095505209287</v>
+        <v>17758.83666286462</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1249,7 +1249,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="6">
-        <v>213217.14606251143</v>
+        <v>213106.03995437548</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1484,19 +1484,19 @@
         <v>60</v>
       </c>
       <c r="B13" s="16">
-        <v>-213217.14606251143</v>
+        <v>-213106.03995437548</v>
       </c>
       <c r="C13" s="16">
-        <v>-213217.14606251143</v>
+        <v>-213106.03995437548</v>
       </c>
       <c r="D13" s="16">
-        <v>-213217.14606251143</v>
+        <v>-213106.03995437548</v>
       </c>
       <c r="E13" s="16">
-        <v>-213217.14606251143</v>
+        <v>-213106.03995437548</v>
       </c>
       <c r="F13" s="16">
-        <v>-213217.14606251143</v>
+        <v>-213106.03995437548</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1504,19 +1504,19 @@
         <v>61</v>
       </c>
       <c r="B14" s="18">
-        <v>-9517.146062511427</v>
+        <v>-9406.039954375476</v>
       </c>
       <c r="C14" s="18">
-        <v>-3406.146062511427</v>
+        <v>-3295.0399543754756</v>
       </c>
       <c r="D14" s="18">
-        <v>2888.1839374885603</v>
+        <v>2999.2900456245115</v>
       </c>
       <c r="E14" s="18">
-        <v>9371.343837488588</v>
+        <v>9482.44994562454</v>
       </c>
       <c r="F14" s="18">
-        <v>16048.998534488608</v>
+        <v>16160.10464262456</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1660,19 +1660,19 @@
         <v>68</v>
       </c>
       <c r="B9" s="16">
-        <v>-2588054.0987622873</v>
+        <v>-2586705.4801175445</v>
       </c>
       <c r="C9" s="16">
-        <v>-2541695.5340621993</v>
+        <v>-2540371.072572721</v>
       </c>
       <c r="D9" s="16">
-        <v>-2492232.250427966</v>
+        <v>-2490933.5639431803</v>
       </c>
       <c r="E9" s="16">
-        <v>-2439456.319082621</v>
+        <v>-2438185.133802328</v>
       </c>
       <c r="F9" s="16">
-        <v>-2383145.8858739194</v>
+        <v>-2381904.0436047153</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1680,19 +1680,19 @@
         <v>69</v>
       </c>
       <c r="B10" s="18">
-        <v>878495.9012377127</v>
+        <v>879844.5198824555</v>
       </c>
       <c r="C10" s="18">
-        <v>1028404.4659378007</v>
+        <v>1029728.9274272788</v>
       </c>
       <c r="D10" s="18">
-        <v>1185217.749572034</v>
+        <v>1186516.4360568197</v>
       </c>
       <c r="E10" s="18">
-        <v>1348193.680917379</v>
+        <v>1349464.8661976722</v>
       </c>
       <c r="F10" s="18">
-        <v>1518504.1141260806</v>
+        <v>1519745.9563952847</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1730,19 +1730,19 @@
         <v>71</v>
       </c>
       <c r="B13" s="21">
-        <v>0.7092502326013393</v>
+        <v>0.7088806467847477</v>
       </c>
       <c r="C13" s="21">
-        <v>0.6763426115120275</v>
+        <v>0.6759901736489412</v>
       </c>
       <c r="D13" s="21">
-        <v>0.6438212995163952</v>
+        <v>0.6434858083035857</v>
       </c>
       <c r="E13" s="21">
-        <v>0.6118526007230051</v>
+        <v>0.6115337681972229</v>
       </c>
       <c r="F13" s="21">
-        <v>0.5802643988005647</v>
+        <v>0.5799620266872937</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1750,19 +1750,19 @@
         <v>72</v>
       </c>
       <c r="B14" s="22">
-        <v>0.9553640678610286</v>
+        <v>0.9558621615962211</v>
       </c>
       <c r="C14" s="22">
-        <v>0.9840249898968594</v>
+        <v>0.9845380264441077</v>
       </c>
       <c r="D14" s="22">
-        <v>1.013545739593765</v>
+        <v>1.014074167237431</v>
       </c>
       <c r="E14" s="22">
-        <v>1.0439521117815782</v>
+        <v>1.044496392254554</v>
       </c>
       <c r="F14" s="22">
-        <v>1.0752706751350256</v>
+        <v>1.0758312840221906</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1770,19 +1770,19 @@
         <v>73</v>
       </c>
       <c r="B15" s="21">
-        <v>0.0774082392376777</v>
+        <v>0.07744859721252062</v>
       </c>
       <c r="C15" s="21">
-        <v>0.07973048641480802</v>
+        <v>0.07977205512889624</v>
       </c>
       <c r="D15" s="21">
-        <v>0.08212240100725227</v>
+        <v>0.08216521678276312</v>
       </c>
       <c r="E15" s="21">
-        <v>0.08458607303746984</v>
+        <v>0.08463017328624603</v>
       </c>
       <c r="F15" s="21">
-        <v>0.08712365522859394</v>
+        <v>0.0871690784848334</v>
       </c>
     </row>
   </sheetData>
@@ -1858,19 +1858,19 @@
         <v>75</v>
       </c>
       <c r="B5" s="21">
-        <v>-0.006594118038220336</v>
+        <v>-0.006520534072868571</v>
       </c>
       <c r="C5" s="21">
-        <v>-0.002360006775570363</v>
+        <v>-0.0022842152912580455</v>
       </c>
       <c r="D5" s="21">
-        <v>0.0020011278249590994</v>
+        <v>0.0020791930538007868</v>
       </c>
       <c r="E5" s="21">
-        <v>0.006493096463504475</v>
+        <v>0.0065735036492114126</v>
       </c>
       <c r="F5" s="21">
-        <v>0.011119824161206205</v>
+        <v>0.01120264356248435</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1878,19 +1878,19 @@
         <v>76</v>
       </c>
       <c r="B6" s="21">
-        <v>-0.010833455283175164</v>
+        <v>-0.01069057059721426</v>
       </c>
       <c r="C6" s="21">
-        <v>-0.003312068524911905</v>
+        <v>-0.003199910060415562</v>
       </c>
       <c r="D6" s="21">
-        <v>0.002436838242197642</v>
+        <v>0.002527811629472347</v>
       </c>
       <c r="E6" s="21">
-        <v>0.006951036761358986</v>
+        <v>0.007026822396897833</v>
       </c>
       <c r="F6" s="21">
-        <v>0.010568952948622744</v>
+        <v>0.010633424997527237</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1898,19 +1898,19 @@
         <v>77</v>
       </c>
       <c r="B7" s="23">
-        <v>0.6020868490084884</v>
+        <v>0.6034126788996631</v>
       </c>
       <c r="C7" s="23">
-        <v>0.7035935648911302</v>
+        <v>0.705032592352097</v>
       </c>
       <c r="D7" s="23">
-        <v>0.814245468426911</v>
+        <v>0.8158013399025836</v>
       </c>
       <c r="E7" s="23">
-        <v>0.9336592368672105</v>
+        <v>0.9353353238397419</v>
       </c>
       <c r="F7" s="23">
-        <v>1.0627815685387687</v>
+        <v>1.064581655924115</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1918,19 +1918,19 @@
         <v>78</v>
       </c>
       <c r="B8" s="21">
-        <v>-0.0934220248386362</v>
+        <v>-0.09294936648241905</v>
       </c>
       <c r="C8" s="21">
-        <v>-0.008251439569957966</v>
+        <v>-0.007986211823047477</v>
       </c>
       <c r="D8" s="21">
-        <v>0.021930129323681408</v>
+        <v>0.022116921226778392</v>
       </c>
       <c r="E8" s="21">
-        <v>0.03732227281294637</v>
+        <v>0.037468008101472286</v>
       </c>
       <c r="F8" s="21">
-        <v>0.04667567404543167</v>
+        <v>0.04679619805728441</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1958,19 +1958,19 @@
         <v>80</v>
       </c>
       <c r="B10" s="24">
-        <v>-0.3979131509913574</v>
+        <v>-0.39658732110065686</v>
       </c>
       <c r="C10" s="24">
-        <v>-0.16056427009556162</v>
+        <v>-0.1597178817555127</v>
       </c>
       <c r="D10" s="24">
-        <v>-0.06582432277916744</v>
+        <v>-0.06523912217859126</v>
       </c>
       <c r="E10" s="24">
-        <v>-0.016916016324177628</v>
+        <v>-0.01647971129354117</v>
       </c>
       <c r="F10" s="24">
-        <v>0.012197738477209842</v>
+        <v>0.012540741337868443</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1978,19 +1978,19 @@
         <v>81</v>
       </c>
       <c r="B11" s="21">
-        <v>-0.3045</v>
+        <v>-0.3037</v>
       </c>
       <c r="C11" s="21">
-        <v>-0.1523</v>
+        <v>-0.1517</v>
       </c>
       <c r="D11" s="21">
-        <v>-0.0877</v>
+        <v>-0.08729999999999999</v>
       </c>
       <c r="E11" s="21">
-        <v>-0.0542</v>
+        <v>-0.054</v>
       </c>
       <c r="F11" s="21">
-        <v>-0.034499999999999996</v>
+        <v>-0.0343</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2084,19 +2084,19 @@
         <v>18</v>
       </c>
       <c r="B6" s="18">
-        <v>3643619</v>
+        <v>3641721</v>
       </c>
       <c r="C6" s="18">
-        <v>3846043</v>
+        <v>3844038</v>
       </c>
       <c r="D6" s="18">
-        <v>4048466</v>
+        <v>4046356</v>
       </c>
       <c r="E6" s="18">
-        <v>4250889</v>
+        <v>4248674</v>
       </c>
       <c r="F6" s="18">
-        <v>4453312</v>
+        <v>4450992</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2104,19 +2104,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="21">
-        <v>0.05590595504085361</v>
+        <v>0.055935092226999265</v>
       </c>
       <c r="C7" s="21">
-        <v>0.052963526408831105</v>
+        <v>0.05299115149225892</v>
       </c>
       <c r="D7" s="21">
-        <v>0.05031535401310027</v>
+        <v>0.05034159129844235</v>
       </c>
       <c r="E7" s="21">
-        <v>0.047919388156218615</v>
+        <v>0.04794437040827326</v>
       </c>
       <c r="F7" s="21">
-        <v>0.04574123708377046</v>
+        <v>0.04576507888578546</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,19 +2124,19 @@
         <v>90</v>
       </c>
       <c r="B8" s="16">
-        <v>2368352.35</v>
+        <v>2367118.65</v>
       </c>
       <c r="C8" s="16">
-        <v>2499927.95</v>
+        <v>2498624.7</v>
       </c>
       <c r="D8" s="16">
-        <v>2631502.9</v>
+        <v>2630131.4</v>
       </c>
       <c r="E8" s="16">
-        <v>2763077.85</v>
+        <v>2761638.1</v>
       </c>
       <c r="F8" s="16">
-        <v>2894652.8000000003</v>
+        <v>2893144.8000000003</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2144,19 +2144,19 @@
         <v>20</v>
       </c>
       <c r="B9" s="16">
-        <v>1298950.1735</v>
+        <v>1298273.5365</v>
       </c>
       <c r="C9" s="16">
-        <v>1371114.3295</v>
+        <v>1370399.5469999998</v>
       </c>
       <c r="D9" s="16">
-        <v>1443278.1290000002</v>
+        <v>1442525.9139999999</v>
       </c>
       <c r="E9" s="16">
-        <v>1515441.9285</v>
+        <v>1514652.281</v>
       </c>
       <c r="F9" s="16">
-        <v>1587605.7279999997</v>
+        <v>1586778.6479999996</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2164,19 +2164,19 @@
         <v>91</v>
       </c>
       <c r="B10" s="21">
-        <v>0.05590595504085361</v>
+        <v>0.055935092226999265</v>
       </c>
       <c r="C10" s="21">
-        <v>0.052963526408831105</v>
+        <v>0.05299115149225892</v>
       </c>
       <c r="D10" s="21">
-        <v>0.05031535401310027</v>
+        <v>0.05034159129844235</v>
       </c>
       <c r="E10" s="21">
-        <v>0.047919388156218615</v>
+        <v>0.04794437040827326</v>
       </c>
       <c r="F10" s="21">
-        <v>0.04574123708377046</v>
+        <v>0.04576507888578546</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2184,19 +2184,19 @@
         <v>92</v>
       </c>
       <c r="B11" s="21">
-        <v>0.05758313369207922</v>
+        <v>0.05761314499380925</v>
       </c>
       <c r="C11" s="21">
-        <v>0.054552432201096034</v>
+        <v>0.05458088603702669</v>
       </c>
       <c r="D11" s="21">
-        <v>0.051824814633493275</v>
+        <v>0.051851839037395625</v>
       </c>
       <c r="E11" s="21">
-        <v>0.049356969800905176</v>
+        <v>0.04938270152052146</v>
       </c>
       <c r="F11" s="21">
-        <v>0.047113474196283575</v>
+        <v>0.047138031252359026</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2204,19 +2204,19 @@
         <v>93</v>
       </c>
       <c r="B12" s="21">
-        <v>0.059310627702841595</v>
+        <v>0.05934153934362352</v>
       </c>
       <c r="C12" s="21">
-        <v>0.056189005167128915</v>
+        <v>0.056218312618137485</v>
       </c>
       <c r="D12" s="21">
-        <v>0.05337955907249808</v>
+        <v>0.053407394208517485</v>
       </c>
       <c r="E12" s="21">
-        <v>0.05083767889493233</v>
+        <v>0.0508641825661371</v>
       </c>
       <c r="F12" s="21">
-        <v>0.04852687842217208</v>
+        <v>0.04855217218992979</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2224,19 +2224,19 @@
         <v>94</v>
       </c>
       <c r="B13" s="21">
-        <v>0.06108994653392685</v>
+        <v>0.061121785523932236</v>
       </c>
       <c r="C13" s="21">
-        <v>0.057874675322142785</v>
+        <v>0.05790486199668162</v>
       </c>
       <c r="D13" s="21">
-        <v>0.05498094584467302</v>
+        <v>0.05500961603477302</v>
       </c>
       <c r="E13" s="21">
-        <v>0.0523628092617803</v>
+        <v>0.05239010804312122</v>
       </c>
       <c r="F13" s="21">
-        <v>0.04998268477483725</v>
+        <v>0.05000873735562769</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2244,19 +2244,19 @@
         <v>95</v>
       </c>
       <c r="B14" s="21">
-        <v>0.06292264492994466</v>
+        <v>0.0629554390896502</v>
       </c>
       <c r="C14" s="21">
-        <v>0.059610915581807075</v>
+        <v>0.05964200785658207</v>
       </c>
       <c r="D14" s="21">
-        <v>0.05663037422001322</v>
+        <v>0.05665990451581621</v>
       </c>
       <c r="E14" s="21">
-        <v>0.05393369353963372</v>
+        <v>0.053961811284414865</v>
       </c>
       <c r="F14" s="21">
-        <v>0.05148216531808237</v>
+        <v>0.05150899947629653</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2264,19 +2264,19 @@
         <v>96</v>
       </c>
       <c r="B15" s="21">
-        <v>0.009087788094635528</v>
+        <v>0.009169519332070757</v>
       </c>
       <c r="C15" s="21">
-        <v>0.0008341313428192113</v>
+        <v>0.0009116210579042463</v>
       </c>
       <c r="D15" s="21">
-        <v>-0.006594122221643123</v>
+        <v>-0.006520525348313302</v>
       </c>
       <c r="E15" s="21">
-        <v>-0.013314924064228404</v>
+        <v>-0.013244847620877385</v>
       </c>
       <c r="F15" s="21">
-        <v>-0.01942474474430742</v>
+        <v>-0.01935786731930042</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2284,19 +2284,19 @@
         <v>97</v>
       </c>
       <c r="B16" s="21">
-        <v>0.013792356541271176</v>
+        <v>0.013876539715829462</v>
       </c>
       <c r="C16" s="21">
-        <v>0.00529109008690037</v>
+        <v>0.005370904493437957</v>
       </c>
       <c r="D16" s="21">
-        <v>-0.0023600110844958356</v>
+        <v>-0.002284206304966119</v>
       </c>
       <c r="E16" s="21">
-        <v>-0.009282436982358673</v>
+        <v>-0.009210258245707124</v>
       </c>
       <c r="F16" s="21">
-        <v>-0.015575552282840056</v>
+        <v>-0.015506668535082847</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2304,19 +2304,19 @@
         <v>98</v>
       </c>
       <c r="B17" s="21">
-        <v>0.018638062041305883</v>
+        <v>0.018724770711100916</v>
       </c>
       <c r="C17" s="21">
-        <v>0.009881757593303954</v>
+        <v>0.00996396643203767</v>
       </c>
       <c r="D17" s="21">
-        <v>0.002001123386765861</v>
+        <v>0.00207920230968147</v>
       </c>
       <c r="E17" s="21">
-        <v>-0.0051289752880328615</v>
+        <v>-0.005054631189281764</v>
       </c>
       <c r="F17" s="21">
-        <v>-0.011610884047528683</v>
+        <v>-0.011539933787338757</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2324,19 +2324,19 @@
         <v>99</v>
       </c>
       <c r="B18" s="21">
-        <v>0.023629138706341663</v>
+        <v>0.023718448636230547</v>
       </c>
       <c r="C18" s="21">
-        <v>0.014610145124899675</v>
+        <v>0.014694820228795404</v>
       </c>
       <c r="D18" s="21">
-        <v>0.006493091892165437</v>
+        <v>0.006573513182768516</v>
       </c>
       <c r="E18" s="21">
-        <v>-0.0008509097428772467</v>
+        <v>-0.0007743353211636164</v>
       </c>
       <c r="F18" s="21">
-        <v>-0.007527275765157942</v>
+        <v>-0.007454196997162319</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2344,19 +2344,19 @@
         <v>100</v>
       </c>
       <c r="B19" s="21">
-        <v>0.02876994767132851</v>
+        <v>0.028861936899114062</v>
       </c>
       <c r="C19" s="21">
-        <v>0.019480384282443263</v>
+        <v>0.019567599639455865</v>
       </c>
       <c r="D19" s="21">
-        <v>0.011119819452726996</v>
+        <v>0.011202653382048167</v>
       </c>
       <c r="E19" s="21">
-        <v>0.0035554977686330304</v>
+        <v>0.0036343694229980703</v>
       </c>
       <c r="F19" s="21">
-        <v>-0.003321159234316085</v>
+        <v>-0.0032458881032805917</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2364,19 +2364,19 @@
         <v>101</v>
       </c>
       <c r="B20" s="21">
-        <v>0.0073089420164296325</v>
+        <v>0.007833933461920604</v>
       </c>
       <c r="C20" s="21">
-        <v>-0.04570749729011211</v>
+        <v>-0.045209750788210885</v>
       </c>
       <c r="D20" s="21">
-        <v>-0.09342205171057717</v>
+        <v>-0.09294931044114041</v>
       </c>
       <c r="E20" s="21">
-        <v>-0.13659236926660184</v>
+        <v>-0.13614224108495568</v>
       </c>
       <c r="F20" s="21">
-        <v>-0.17583811778706174</v>
+        <v>-0.17540853814151186</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2384,19 +2384,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21">
-        <v>0.04686761390042227</v>
+        <v>0.04714786785970959</v>
       </c>
       <c r="C21" s="21">
-        <v>0.018200709392039945</v>
+        <v>0.018473306506108234</v>
       </c>
       <c r="D21" s="21">
-        <v>-0.008251454650890958</v>
+        <v>-0.007986180379738972</v>
       </c>
       <c r="E21" s="21">
-        <v>-0.03275938819749615</v>
+        <v>-0.03250088580344506</v>
       </c>
       <c r="F21" s="21">
-        <v>-0.055549465544855084</v>
+        <v>-0.055297249448209115</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2404,19 +2404,19 @@
         <v>103</v>
       </c>
       <c r="B22" s="21">
-        <v>0.06044857195111973</v>
+        <v>0.06064291895159782</v>
       </c>
       <c r="C22" s="21">
-        <v>0.040489826176738825</v>
+        <v>0.04068036520079933</v>
       </c>
       <c r="D22" s="21">
-        <v>0.021930118701980826</v>
+        <v>0.0221169433706003</v>
       </c>
       <c r="E22" s="21">
-        <v>0.004607205988824428</v>
+        <v>0.004790578490325242</v>
       </c>
       <c r="F22" s="21">
-        <v>-0.011615548715258913</v>
+        <v>-0.011435396493004514</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2424,19 +2424,19 @@
         <v>104</v>
       </c>
       <c r="B23" s="21">
-        <v>0.06727126319346804</v>
+        <v>0.06742185883462001</v>
       </c>
       <c r="C23" s="21">
-        <v>0.051778467569859085</v>
+        <v>0.05192662912358938</v>
       </c>
       <c r="D23" s="21">
-        <v>0.03732226452592857</v>
+        <v>0.03746802537811357</v>
       </c>
       <c r="E23" s="21">
-        <v>0.023784999238844168</v>
+        <v>0.02392852794039351</v>
       </c>
       <c r="F23" s="21">
-        <v>0.011067363971762365</v>
+        <v>0.011208809441008601</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2444,19 +2444,19 @@
         <v>105</v>
       </c>
       <c r="B24" s="21">
-        <v>0.07140126554943418</v>
+        <v>0.07152538613168005</v>
       </c>
       <c r="C24" s="21">
-        <v>0.05862107345451717</v>
+        <v>0.058743398955429696</v>
       </c>
       <c r="D24" s="21">
-        <v>0.04667566719178516</v>
+        <v>0.04679621234425556</v>
       </c>
       <c r="E24" s="21">
-        <v>0.03547111764527228</v>
+        <v>0.03559000978814668</v>
       </c>
       <c r="F24" s="21">
-        <v>0.024928093704951023</v>
+        <v>0.025045445052029793</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2464,19 +2464,19 @@
         <v>106</v>
       </c>
       <c r="B25" s="21">
-        <v>-0.11535784424574194</v>
+        <v>-0.11388521747032529</v>
       </c>
       <c r="C25" s="21">
-        <v>-0.2640715589894407</v>
+        <v>-0.2626753556177443</v>
       </c>
       <c r="D25" s="21">
-        <v>-0.39791322636802173</v>
+        <v>-0.396587163902397</v>
       </c>
       <c r="E25" s="21">
-        <v>-0.5190080862737801</v>
+        <v>-0.517745454627744</v>
       </c>
       <c r="F25" s="21">
-        <v>-0.6290943373833734</v>
+        <v>-0.6278893453894705</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2484,19 +2484,19 @@
         <v>107</v>
       </c>
       <c r="B26" s="21">
-        <v>0.005146673332176806</v>
+        <v>0.0059452948328749065</v>
       </c>
       <c r="C26" s="21">
-        <v>-0.07869835182556251</v>
+        <v>-0.07787919190940973</v>
       </c>
       <c r="D26" s="21">
-        <v>-0.16056431823649392</v>
+        <v>-0.1597177814478668</v>
       </c>
       <c r="E26" s="21">
-        <v>-0.2414653599729104</v>
+        <v>-0.2405814035379224</v>
       </c>
       <c r="F26" s="21">
-        <v>-0.32254898917894903</v>
+        <v>-0.3216136301142991</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2504,19 +2504,19 @@
         <v>108</v>
       </c>
       <c r="B27" s="21">
-        <v>0.046882663316869896</v>
+        <v>0.047416959365686046</v>
       </c>
       <c r="C27" s="21">
-        <v>-0.00967928199537036</v>
+        <v>-0.00912212639595596</v>
       </c>
       <c r="D27" s="21">
-        <v>-0.06582435606741147</v>
+        <v>-0.06523905283107681</v>
       </c>
       <c r="E27" s="21">
-        <v>-0.12221895558556642</v>
+        <v>-0.12159787764097411</v>
       </c>
       <c r="F27" s="21">
-        <v>-0.1796360597644724</v>
+        <v>-0.17896880569165957</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2524,19 +2524,19 @@
         <v>109</v>
       </c>
       <c r="B28" s="21">
-        <v>0.06696093154439192</v>
+        <v>0.06735759231133781</v>
       </c>
       <c r="C28" s="21">
-        <v>0.024912501272786162</v>
+        <v>0.025327196690801874</v>
       </c>
       <c r="D28" s="21">
-        <v>-0.016916041142728946</v>
+        <v>-0.016479659591118898</v>
       </c>
       <c r="E28" s="21">
-        <v>-0.058975537434400496</v>
+        <v>-0.05851230726819558</v>
       </c>
       <c r="F28" s="21">
-        <v>-0.10177372055543471</v>
+        <v>-0.10127685229550934</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2544,19 +2544,19 @@
         <v>110</v>
       </c>
       <c r="B29" s="21">
-        <v>0.07832878170191793</v>
+        <v>0.0786422401955287</v>
       </c>
       <c r="C29" s="21">
-        <v>0.04513398010420104</v>
+        <v>0.045460989948092834</v>
       </c>
       <c r="D29" s="21">
-        <v>0.01219771896677271</v>
+        <v>0.012540781984477082</v>
       </c>
       <c r="E29" s="21">
-        <v>-0.02079942181324558</v>
+        <v>-0.020436821361201278</v>
       </c>
       <c r="F29" s="21">
-        <v>-0.054202423619151105</v>
+        <v>-0.05381586624455126</v>
       </c>
     </row>
   </sheetData>
